--- a/maintenance/WOD_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/WOD_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,26 @@
           <t>Last_Done_Draw</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +633,22 @@
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Resin line seals; Resin line cleaning solvent; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +728,22 @@
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Resin line seals; Resin line cleaning solvent; Purge gas / line flush consumables</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +823,22 @@
         <v>0</v>
       </c>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Applicator seal kit; IPA wipes / cleaning cloth; Purge gas / line flush consumables</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +918,18 @@
         <v>0</v>
       </c>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -935,6 +1015,22 @@
         <v>0</v>
       </c>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Applicator seal kit</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1020,6 +1116,22 @@
         <v>0</v>
       </c>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth; Purge gas / line flush consumables</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1105,6 +1217,18 @@
         <v>0</v>
       </c>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1190,6 +1314,22 @@
         <v>0</v>
       </c>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Applicator seal kit</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/maintenance/WOD_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/WOD_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,21 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,9 +609,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Wet on Dry Coating System Manual (Soreq)</t>
@@ -620,19 +632,20 @@
           <t>Avoid excessive ambient UV light near vessels (risk of pre-curing). Keep opening times minimal.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>Resin line seals; Resin line cleaning solvent; IPA wipes / cleaning cloth</t>
@@ -648,6 +661,15 @@
       </c>
       <c r="Y2" t="n">
         <v>20</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -689,9 +711,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Wet on Dry Coating System Manual (Soreq)</t>
@@ -715,19 +734,20 @@
           <t>Capture resin run-off from dip tube during lid removal; prevent contamination transfer into vessel.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U3" t="n">
+        <v>93</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>Resin line seals; Resin line cleaning solvent; Purge gas / line flush consumables</t>
@@ -743,6 +763,15 @@
       </c>
       <c r="Y3" t="n">
         <v>25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="4">
@@ -784,9 +813,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Wet on Dry Coating System Manual (Soreq)</t>
@@ -810,19 +836,20 @@
           <t>Keep pressure low to avoid overflow. Keep delivery block covered with clean light-proof cover when exposed.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U4" t="n">
+        <v>93</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>Applicator seal kit; IPA wipes / cleaning cloth; Purge gas / line flush consumables</t>
@@ -838,6 +865,15 @@
       </c>
       <c r="Y4" t="n">
         <v>20</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="5">
@@ -879,9 +915,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Wet on Dry Coating System Manual (Soreq)</t>
@@ -905,20 +938,20 @@
           <t>Do not allow coating to overflow into bubble stripper cap.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U5" t="n">
+        <v>93</v>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Routine</t>
@@ -929,6 +962,15 @@
       </c>
       <c r="Y5" t="n">
         <v>20</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="6">
@@ -970,7 +1012,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>days</t>
@@ -1002,19 +1043,14 @@
           <t>Levelness affects concentricity and coating stability.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
+          <t>2026-04-04</t>
+        </is>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Applicator seal kit</t>
@@ -1071,7 +1107,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -1103,19 +1138,14 @@
           <t>Whenever a VCO/VCR joint is undone, replace the O-ring/gasket and purge the line thoroughly.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
+          <t>2026-03-29</t>
+        </is>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>IPA wipes / cleaning cloth; Purge gas / line flush consumables</t>
@@ -1172,7 +1202,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -1204,20 +1233,14 @@
           <t>Use correct inhibitor mix; fix leaks immediately.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
+          <t>2026-04-02</t>
+        </is>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Weekly</t>
@@ -1269,7 +1292,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>months</t>
@@ -1301,19 +1323,14 @@
           <t>Misalignment introduces lateral force and can degrade coating concentricity.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
+          <t>2026-03-17</t>
+        </is>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
-      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Applicator seal kit</t>
